--- a/Pathfinder_Cost_Summary_PT.xlsx
+++ b/Pathfinder_Cost_Summary_PT.xlsx
@@ -8279,7 +8279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -8453,49 +8453,49 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12">
-        <f> CUSTO FINAL (com TP)</f>
-        <v/>
-      </c>
-      <c r="B16" s="13">
-        <f>SUM(B10:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="14">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Supermetal - GDT Integration/Assembly (modificação do vagão, custo direto)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>707790.6</v>
+      </c>
+      <c r="C16" s="3">
         <f>B16/$B$3</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>CUSTO FINAL (com TP):</t>
+        </is>
+      </c>
+      <c r="B17" s="13">
+        <f>SUM(B10:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="14">
+        <f>B17/$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>2) MARGEM (TDM aplicado sobre o custo SEM o TP; TP é devolvido depois sem markup)</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Base p/ margem (Custo Final - TP)</t>
-        </is>
-      </c>
-      <c r="B19" s="4">
-        <f>B16-B12</f>
-        <v/>
-      </c>
-      <c r="C19" s="3">
-        <f>B19/$B$3</f>
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Preço Líquido s/ TP (Base / (1 - TDM))</t>
+          <t>Base p/ margem (Custo Final - TP)</t>
         </is>
       </c>
       <c r="B20" s="4">
-        <f>B19/(1-$B$4)</f>
+        <f>B17-B12</f>
         <v/>
       </c>
       <c r="C20" s="3">
@@ -8504,49 +8504,50 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12">
-        <f> PREÇO LÍQUIDO ('NOSSO PREÇO' - custo + margem, sem impostos de saída)</f>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preço Líquido s/ TP (Base / (1 - TDM))</t>
+        </is>
+      </c>
+      <c r="B21" s="4">
+        <f>B20/(1-$B$4)</f>
         <v/>
       </c>
-      <c r="B21" s="13">
-        <f>B20+B12</f>
-        <v/>
-      </c>
-      <c r="C21" s="14">
+      <c r="C21" s="3">
         <f>B21/$B$3</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO LÍQUIDO ('NOSSO PREÇO' - custo + margem, sem impostos de saída):</t>
+        </is>
+      </c>
+      <c r="B22" s="13">
+        <f>B21+B12</f>
+        <v/>
+      </c>
+      <c r="C22" s="14">
+        <f>B22/$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>3) IMPOSTOS DE SAÍDA (não afetam nossa margem - o cliente paga, cliente pode creditar parte)</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>+ PIS/COFINS (por dentro)</t>
-        </is>
-      </c>
-      <c r="B24" s="4">
-        <f>B21/(1-$B$5)</f>
-        <v/>
-      </c>
-      <c r="C24" s="3">
-        <f>B24/$B$3</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>+ ICMS (por dentro, empilhado sobre PIS/COFINS)</t>
+          <t>+ PIS/COFINS (por dentro)</t>
         </is>
       </c>
       <c r="B25" s="4">
-        <f>B24/(1-$B$6)</f>
+        <f>B22/(1-$B$5)</f>
         <v/>
       </c>
       <c r="C25" s="3">
@@ -8557,11 +8558,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>+ IPI (por fora, % sobre o valor já com ICMS)</t>
+          <t>+ ICMS (por dentro, empilhado sobre PIS/COFINS)</t>
         </is>
       </c>
       <c r="B26" s="4">
-        <f>B25*$B$7</f>
+        <f>B25/(1-$B$6)</f>
         <v/>
       </c>
       <c r="C26" s="3">
@@ -8570,84 +8571,108 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12">
-        <f> PREÇO FINAL AO CLIENTE (com todos os impostos)</f>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>+ IPI (por fora, % sobre o valor já com ICMS)</t>
+        </is>
+      </c>
+      <c r="B27" s="4">
+        <f>B26*$B$7</f>
         <v/>
       </c>
-      <c r="B27" s="13">
-        <f>B25+B26</f>
-        <v/>
-      </c>
-      <c r="C27" s="14">
+      <c r="C27" s="3">
         <f>B27/$B$3</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO FINAL AO CLIENTE (com todos os impostos):</t>
+        </is>
+      </c>
+      <c r="B28" s="13">
+        <f>B26+B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="14">
+        <f>B28/$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Notas / Premissas:</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>- Metodologia: abas 'Material Pricing' + 'Approval Summary' do Material Pricing.xlsm (P&amp;L Old descartado - fórmulas quebradas/#REF!).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>- TP tratado como a margem da WBT USA (GM WBT USA); entra no custo mas fica fora da base de margem da WBT Brasil (TDM = (TP + GM BRZ) / Preço Líquido).</t>
+          <t>- Metodologia: abas 'Material Pricing' + 'Approval Summary' do Material Pricing.xlsm (P&amp;L Old descartado - fórmulas quebradas/#REF!).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>- Frete Internacional e Frete Nacional: valores reais da cotação China Gate (Planilha de Custos de Importação - Pathfinder - Set 26.xlsx), não os 9%/3% antigos.</t>
+          <t>- TP tratado como a margem da WBT USA (GM WBT USA); entra no custo mas fica fora da base de margem da WBT Brasil (TDM = (TP + GM BRZ) / Preço Líquido).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>- II/IPI/PIS-COFINS: taxa real por NCM (aba 'II' da Material Pricing) para os 6 itens com NCM confirmado; taxa 'pior caso' (nossa antiga flat) para os demais 41 sem NCM.</t>
+          <t>- Frete Internacional e Frete Nacional: valores reais da cotação China Gate (Planilha de Custos de Importação - Pathfinder - Set 26.xlsx), não os 9%/3% antigos.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>- ICMS: 18% flat (mesmo valor usado no exemplo real da Material Pricing).</t>
+          <t>- II/IPI/PIS-COFINS: taxa real por NCM (aba 'II' da Material Pricing) para os 6 itens com NCM confirmado; taxa 'pior caso' (nossa antiga flat) para os demais 41 sem NCM.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>- 88 itens PAC somados como um bloco só (já é custo all-in local, sem decompor TP/frete/II).</t>
+          <t>- ICMS: 18% flat (mesmo valor usado no exemplo real da Material Pricing).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>- 27 itens ainda sem cotação de custo (Missing) NÃO estão incluídos neste total - ver aba Lista de Itens (Fonte do Custo = MISSING).</t>
+          <t>- 88 itens PAC somados como um bloco só (já é custo all-in local, sem decompor TP/frete/II).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
+          <t>- Custo da Supermetal (Integração/Montagem GDT: reforma do vagão - teto, porta, escada, chicotes, skid de baterias, tubulação Fastbrake, ar condicionado, lastro) incluído como custo direto, entrando na mesma base de margem do equipamento - ver aba 'GDT Integration and Assembly' no arquivo de trabalho principal para o detalhamento item a item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>- 27 itens ainda sem cotação de custo (Missing) NÃO estão incluídos neste total - ver aba Lista de Itens (Fonte do Custo = MISSING).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
           <t>- QQP (tributos de serviço) e ISS (imposto do rollup GDT de integração/labor) foram desconsiderados por enquanto, a pedido.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A36:F36"/>
@@ -8656,7 +8681,7 @@
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pathfinder_Cost_Summary_PT.xlsx
+++ b/Pathfinder_Cost_Summary_PT.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lista de Itens" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo Executivo (P&amp;L)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalhamento do Preço" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de Itens'!$A$3:$M$165</definedName>
@@ -57,7 +58,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +75,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -121,6 +128,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -624,7 +640,6 @@
           <t>90328990</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -667,7 +682,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -710,7 +724,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -753,7 +766,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -796,7 +808,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -839,7 +850,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -882,7 +892,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -925,7 +934,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -968,7 +976,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1016,7 +1023,6 @@
           <t>85371090</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1059,7 +1065,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1102,7 +1107,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1145,7 +1149,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1188,7 +1191,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1231,7 +1233,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1284,7 +1285,6 @@
           <t>24x10x20</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1337,7 +1337,6 @@
           <t>20x3.5x25.5</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1380,7 +1379,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -1418,7 +1416,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -1456,7 +1453,6 @@
           <t>High</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1509,7 +1505,6 @@
           <t>18.5x8.5x15</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1562,7 +1557,6 @@
           <t>18.5x8.5x15</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1615,7 +1609,6 @@
           <t>14.25x14.25x10</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1668,7 +1661,6 @@
           <t>17.2x1.95x11.2</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1711,7 +1703,6 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1762,7 +1753,6 @@
           <t>14x6x8.5</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1855,7 +1845,6 @@
         <v>761</v>
       </c>
       <c r="H31" s="4" t="n"/>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1906,7 +1895,6 @@
           <t>20.5x10.5x11.5</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1954,7 +1942,6 @@
           <t>85381000</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2007,7 +1994,6 @@
           <t>3.5x0.75x0.75</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2042,7 +2028,6 @@
         <v>411.22</v>
       </c>
       <c r="H35" s="4" t="n"/>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2077,7 +2062,6 @@
         <v>404.6239</v>
       </c>
       <c r="H36" s="4" t="n"/>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2130,7 +2114,6 @@
           <t>7x4x7</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2184,7 +2167,6 @@
           <t>11.8x6.4x8.05</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2237,7 +2219,6 @@
           <t>12.8x3.8x9.5</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2290,7 +2271,6 @@
           <t>8.4x3.35x7.5</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2343,7 +2323,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2396,7 +2375,6 @@
           <t>13.5x5.25x7</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2431,7 +2409,6 @@
         <v>205</v>
       </c>
       <c r="H43" s="4" t="n"/>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2484,7 +2461,6 @@
           <t>24x20x24</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2519,7 +2495,6 @@
         <v>171.544</v>
       </c>
       <c r="H45" s="4" t="n"/>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2554,7 +2529,6 @@
         <v>159</v>
       </c>
       <c r="H46" s="4" t="n"/>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2607,7 +2581,6 @@
           <t>3x2x3</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2660,7 +2633,6 @@
           <t>6x2.25x3</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2713,7 +2685,6 @@
           <t>9.35x5.3x5.2</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2766,7 +2737,6 @@
           <t>3.875x1.625x2.125</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2819,7 +2789,6 @@
           <t>3x0.75x1.5</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2872,7 +2841,6 @@
           <t>7x3.25x4.75</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2925,7 +2893,6 @@
           <t>5.2x2.9x3.35</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2978,7 +2945,6 @@
           <t>4.52x1.35x6.95</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3031,7 +2997,6 @@
           <t>12x0.5x0.5</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3084,7 +3049,6 @@
           <t>4x2.5x2.5</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3139,7 +3103,6 @@
           <t>2.9x0.5x0.5</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3187,7 +3150,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3240,7 +3202,6 @@
           <t>1.75x3.25x2.75</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3293,7 +3254,6 @@
           <t>9.5x1.5x9.5</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3347,7 +3307,6 @@
           <t>2x1x1</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3400,7 +3359,6 @@
           <t>1x0.125x0.125</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3453,7 +3411,6 @@
           <t>12x3x7.5</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3488,7 +3445,6 @@
         <v>79.83</v>
       </c>
       <c r="H64" s="4" t="n"/>
-      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3541,7 +3497,6 @@
           <t>2.5x1.5x1.5</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3589,7 +3544,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3624,7 +3578,6 @@
         <v>72.41</v>
       </c>
       <c r="H67" s="4" t="n"/>
-      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3659,7 +3612,6 @@
         <v>71.94</v>
       </c>
       <c r="H68" s="4" t="n"/>
-      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3694,7 +3646,6 @@
         <v>71.94</v>
       </c>
       <c r="H69" s="4" t="n"/>
-      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3742,7 +3693,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3795,7 +3745,6 @@
           <t>4x2.125x2.125</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3848,7 +3797,6 @@
           <t>1.95x2.7x1.8</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3901,7 +3849,6 @@
           <t>4.75x1.25x4</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3949,7 +3896,6 @@
           <t>1.5x1x1.5</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3984,7 +3930,6 @@
         <v>59.75</v>
       </c>
       <c r="H75" s="4" t="n"/>
-      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4032,7 +3977,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4080,7 +4024,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4134,7 +4077,6 @@
           <t>4x2x4</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4182,7 +4124,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4235,7 +4176,6 @@
           <t>5.85x1.95x3.9</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4283,7 +4223,6 @@
           <t>3.95x1.25x6.65</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4337,7 +4276,6 @@
           <t>4x2x3</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4390,7 +4328,6 @@
           <t>3.1x0.7x2.45</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4443,7 +4380,6 @@
           <t>3x2x2.55</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4497,7 +4433,6 @@
           <t>2.9x2.45x3.05</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4545,7 +4480,6 @@
           <t>85359090</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4598,7 +4532,6 @@
           <t>9x1.5x9</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4652,7 +4585,6 @@
           <t>4x1x4</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4700,7 +4632,6 @@
           <t>0x0x0</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4736,7 +4667,6 @@
         <v>45.7356</v>
       </c>
       <c r="H90" s="4" t="n"/>
-      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4789,7 +4719,6 @@
           <t>4.5x5.25x4.5</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4842,7 +4771,6 @@
           <t>5.8x3.5x4.5</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4895,7 +4823,6 @@
           <t>3x1x2</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4948,7 +4875,6 @@
           <t>0.75x0.1x0.1</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5002,7 +4928,6 @@
           <t>2.5x1.25x1.25</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5056,7 +4981,6 @@
           <t>3.5x2x3.25</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5109,7 +5033,6 @@
           <t>17x1.25x12.625</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5162,7 +5085,6 @@
           <t>2.5x0.65x3.05</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5215,7 +5137,6 @@
           <t>1x0.001x0.001</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5269,7 +5190,6 @@
           <t>3.1x1.45x2.5</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5323,7 +5243,6 @@
           <t>2.5x1.5x3.25</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5376,7 +5295,6 @@
           <t>2.5x1.5x2.5</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5429,7 +5347,6 @@
           <t>2.5x1.5x3</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5482,7 +5399,6 @@
           <t>2.5x1.5x3.25</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5535,7 +5451,6 @@
           <t>3.1x1.45x2.5</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5588,7 +5503,6 @@
           <t>3x1.5x2.5</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5641,7 +5555,6 @@
           <t>6.375x6.375x1.5</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5694,7 +5607,6 @@
           <t>3.05x2.2x4.7</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5747,7 +5659,6 @@
           <t>12.75x3.375x2.75</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5800,7 +5711,6 @@
           <t>8.125x1.625x2</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5835,7 +5745,6 @@
         <v>13.66</v>
       </c>
       <c r="H111" s="4" t="n"/>
-      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5888,7 +5797,6 @@
           <t>1.7x0.95x1.75</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5941,7 +5849,6 @@
           <t>2x1x2</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5994,7 +5901,6 @@
           <t>0.125x0.125x0.25</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6048,7 +5954,6 @@
           <t>4.5x1.48x1.48</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6101,7 +6006,6 @@
           <t>3.05x0.7x2.45</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6154,7 +6058,6 @@
           <t>2.5x1x1</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6207,7 +6110,6 @@
           <t>1x0.001x0.001</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6260,7 +6162,6 @@
           <t>3.75x4.15x7.5</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6313,7 +6214,6 @@
           <t>1.75x0.375x1.75</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6366,7 +6266,6 @@
           <t>1.55x1x1</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6419,7 +6318,6 @@
           <t>1.25x0.75x0.75</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6472,7 +6370,6 @@
           <t>2x1x1</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6525,7 +6422,6 @@
           <t>5.1x1.15x2.95</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6581,7 +6477,6 @@
           <t>1x0.1x0.1</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6634,7 +6529,6 @@
           <t>1.125x0.25x0.25</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6687,7 +6581,6 @@
           <t>5.1x1.15x2.95</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6740,7 +6633,6 @@
           <t>1.65x1.05x1.65</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6794,7 +6686,6 @@
           <t>1.6x1.05x1.7</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6848,7 +6739,6 @@
           <t>1.25x1.05x1.3</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6901,7 +6791,6 @@
           <t>7.1x2.9x6.45</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6954,7 +6843,6 @@
           <t>4x0.5x1</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7007,7 +6895,6 @@
           <t>0.25x0.005x0.25</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7060,7 +6947,6 @@
           <t>0.4x0.3x1</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7113,7 +6999,6 @@
           <t>1.95x0.55x1</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7166,7 +7051,6 @@
           <t>0.85x0.3x1</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7219,7 +7103,6 @@
           <t>0.05x0.05x0.1</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7272,7 +7155,6 @@
           <t>0.05x0.05x0.05</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7307,7 +7189,6 @@
         <v>0.01</v>
       </c>
       <c r="H139" s="4" t="n"/>
-      <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7342,7 +7223,6 @@
         <v>0.01</v>
       </c>
       <c r="H140" s="4" t="n"/>
-      <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8685,4 +8565,948 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DETALHAMENTO DO CÁLCULO DE PREÇO - origem e fórmula de cada número</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Use esta aba pra responder 'por que esse número é X' - cada linha cita a fonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>0) CHECAGEM DE REALIDADE vs. preço doméstico nos EUA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Preço de Referência Doméstico EUA (input - digite o valor real aqui):</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nosso Preço (Líquido - custo + margem, antes dos impostos brasileiros de saída):</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>945272.4347593583</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>&lt;- esse é o número que é de fato comparável a uma venda doméstica nos EUA (sem imposto de importação/consumo do Brasil).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Preço Final ao Cliente (com todos os impostos brasileiros):</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>1405909.269713061</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Diferença vs. referência EUA (Preço Líquido):</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>B6-B5</f>
+        <v/>
+      </c>
+      <c r="C8" s="17">
+        <f>B8/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Diferença vs. referência EUA (Preço Final ao Cliente):</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>B7-B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="17">
+        <f>B9/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>PONTO-CHAVE: nosso Preço Líquido está próximo do preço de referência dos EUA - o salto grande até o Preço Final ao Cliente vem</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>inteiro do Imposto de Importação (II) e dos impostos de consumo brasileiros (IPI/PIS/COFINS/ICMS), que não existem numa venda</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>doméstica nos EUA e incidiriam do mesmo jeito seja importando componentes ou um vagão pronto (um veículo pronto pode inclusive</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>cair numa faixa de II diferente/maior - vale confirmar com um especialista em importação automotiva/ferroviária antes de assumir que 'comprar pronto' evita essa cascata de imposto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>1) CASCATA COMPLETA (bate com a aba 'Resumo Executivo (P&amp;L)', só que com a fonte de cada linha)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Etapa</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Fórmula / Lógica</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Multiplicador Acumulado</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Fonte / Justificativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Raw Cost - Itens Importados</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>BOM USD unitário x Qtd x Câmbio, somado nos 47 itens importados precificados</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1346980.92</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>264113.905882353</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.00x</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>Aba Final Cost List, coluna F (BOM Price USD Unit) x coluna E (Quantity), câmbio da aba 'RATES' do Material Pricing.xlsm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Raw Cost - Itens PAC</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Soma do custo unitário PAC (BRL) x Qtd nos 88 itens PAC</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>166060.16</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>32560.81568627451</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>9.11x</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Campo 'aco_cost' do 7-PAC Item Costs.xlsx por item, já é custo de fabricação local completo (material+mão de obra+overhead)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TP - Transfer Price</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>13% nos itens que já tinham algum TP historicamente; 17,2% nos que não tinham nenhum</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>198163.69</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>38855.62549019608</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8.64x</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Diretriz do Matheus nesta sessão; a divisão 17,2%/0% original veio da cópia colorida de revisão (amarelo/verde)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Frete Internacional</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>1,2295642% sobre (Raw Cost + TP)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>18998.55</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3725.205882352941</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>91.07x</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>'Planilha de Custos de Importação - Pathfinder - Set 26.xlsx' (cotação do despachante China Gate), Frete+Seguro / Valor do Produto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>II - Imposto de Importação</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Blended 17.96% sobre (Raw Cost+TP+Frete): taxa real por NCM pros 6 itens com NCM confirmado, pior caso 18% flat pros outros 41</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>280915.82</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>55081.53333333334</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7.16x</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>Aba 'II' do Material Pricing.xlsm (consulta real por NCM) + nossa taxa flat antiga como fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Frete Nacional</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Cotação real fixa pra remessa inteira (Santos -&gt; Betim/Contagem, MG)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>21753.1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>4265.313725490196</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>93.45x</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Cotação China Gate, aba 'Despesas de Importação': Siscomex, despachante, armazenagem, transporte rodoviário, Marinha Mercante, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Supermetal - Integração/Montagem GDT</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Custo direto: reforma do vagão (teto, porta, escada, chicotes, skid de baterias, tubulação Fastbrake, ar condicionado, lastro)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>707790.6</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>138782.4705882353</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.87x</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>Aba 'GDT Integration and Assembly', soma da coluna Direct Cost BRL (18 itens)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>CUSTO FINAL (com TP):</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>2740662.84</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>537384.8705882353</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>2) MARGEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Base p/ margem</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Custo Final - TP (o TP fica fora da nossa base de margem - é margem da WBT USA, não nossa)</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>Aba Approval Summary do Material Pricing.xlsm: TDM = (TP + GM_BRZ) / Preço Líquido. Algebricamente isso equivale a calcular a margem sobre (custo - TP) e devolver o TP depois, que é o que essa linha faz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Margem alvo (TDM)</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Editável - ver célula B4 da aba Resumo Executivo (P&amp;L)</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Alvo do Matheus pra esse exercício: 45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO LÍQUIDO ('NOSSO PREÇO'):</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>4820889.417272727</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>945272.4347593583</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.759x</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>3) IMPOSTOS DE SAÍDA (o cliente paga; não afetam nossa margem)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PIS/COFINS</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Preço Líquido / (1 - 10.06%) - por dentro, taxa blended real por NCM</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>Aba 'II' do Material Pricing.xlsm (PIS+COFINS real por NCM) pros itens conhecidos, pior caso 9,25% pro resto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ICMS</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>Subtotal anterior / (1 - 18%) - por dentro, empilhado sobre PIS/COFINS</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>18% flat, bate com o exemplo real da Material Pricing. AINDA NÃO validado contra a alíquota de ICMS específica do estado de destino do cliente (as abas Tabela ICMS / Aliquotas Basicas têm a matriz real origem-destino se precisar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IPI</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Subtotal anterior x IPI% blended - somado por fora, não é por dentro</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Aba 'II' do Material Pricing.xlsm (IPI real por NCM) pros itens conhecidos, pior caso 9,75% pro resto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>PREÇO FINAL AO CLIENTE:</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>7170137.27553661</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>1405909.269713061</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2.616x</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>4) REGISTRO DE PREMISSAS (questione um input específico aqui, não o número todo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Premissa</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Valor Usado</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Onde pode estar errado</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Câmbio</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5,10 BRL/USD</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>Foto fixa do Material Pricing.xlsm; vai variar com o câmbio real na data da fatura</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Divisão da taxa de TP</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>13% / 17,2%</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Baixa-Média</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="inlineStr">
+        <is>
+          <t>Divisão arbitrária escolhida nesta sessão, não vem de um documento oficial de política de transfer pricing da Wabtec</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Frete Internacional</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1,23% do valor</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>Cotação real do despachante, mas é só uma simulação pelo próprio aviso da cotação - confirmar com booking real</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Frete Nacional</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>R$21.753,10 fixo</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>Cotação real específica pra Santos-&gt;Betim/Contagem; muda se origem/destino mudar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>II (Imposto de Importação)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>17,96% blended (6 de 47 itens importados com NCM real)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>41 dos 47 itens importados ainda usam o pior caso 18% padrão - sem NCM confirmado pra eles ainda</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PIS/COFINS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10,06% blended</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>Mesma lacuna de cobertura de NCM que o II</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>IPI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>9,69% blended</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Mesma lacuna de cobertura de NCM que o II</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ICMS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>18% flat</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Baixa-Média</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>Não consultado por par origem-destino UF; taxa real pode ser menor (interestadual) ou ter redução RBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Deal Margin (TDM)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>N/A - decisão de negócio</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>Essa é a maior alavanca isolada do preço final - ver tabela de sensibilidade abaixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Itens PAC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tratados como um bloco único all-in, sem decompor TP/frete/duty</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>Custo PAC é genuinamente um custo de fabricação local brasileiro, não uma transação de importação</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Itens faltantes</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>27 itens excluídos (ainda sem custo)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>Preço final vai aumentar quando esses tiverem cotação - ver aba 'Missing Items'</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Supermetal / rollup GDT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Tratado como custo local, sem imposto de importação (correto, é mão de obra+material brasileiro)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>Ainda não inclui ISS (imposto sobre serviço) na parte de mão de obra - desconsiderado por enquanto a pedido do Matheus</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>5) SENSIBILIDADE DA MARGEM (mesma base de custo, TDM diferentes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>TDM</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>Preço Líquido (Nosso Preço) USD</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>Preço Final ao Cliente USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>751040.2613445378</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1117026.612143629</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>805823.6948717949</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1198506.336073469</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>869737.7006535948</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1293566.013991615</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="B60" s="21" t="n">
+        <v>945272.4347593583</v>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>1405909.269713061</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1035914.115686275</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1540721.176578796</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1146698.392374728</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1705491.28497025</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>Notas:</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>- Esta aba é complementar à 'Resumo Executivo (P&amp;L)' - mesmos números, mas cada linha se explica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>- QQP (impostos de serviço) e ISS na parte de mão de obra da Supermetal foram desconsiderados por enquanto, a pedido - o preço final pode aumentar quando isso for incluído.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D49:F49"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Pathfinder_Cost_Summary_PT.xlsx
+++ b/Pathfinder_Cost_Summary_PT.xlsx
@@ -8728,7 +8728,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Multiplicador Acumulado</t>
+          <t>Multiplicador vs. Custo Final (só nos totais)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.00x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F17" s="18" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9.11x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8.64x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>91.07x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7.16x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>93.45x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.87x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
@@ -8944,6 +8944,11 @@
       </c>
       <c r="D24" s="14" t="n">
         <v>537384.8705882353</v>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>1.000x (baseline)</t>
+        </is>
       </c>
     </row>
     <row r="26">

--- a/Pathfinder_Cost_Summary_PT.xlsx
+++ b/Pathfinder_Cost_Summary_PT.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,6 +85,16 @@
     <font>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FFCC0000"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -154,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -208,6 +218,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9617,7 +9633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" style="22" min="1" max="1"/>
@@ -10711,10 +10727,169 @@
         <v>0</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="31" t="inlineStr">
+        <is>
+          <t>6) REFERÊNCIA: UNIDADE PRONTA DOS EUA IMPORTADA COMO ESTÁ (comprar o Pathfinder pronto de US$900 mil e desembaraçar no Brasil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Câmbio usado nessa referência (diferente do câmbio dos cenários acima)</t>
+        </is>
+      </c>
+      <c r="B59" s="43" t="n">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="46" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="C60" s="46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Preço EUA (produto pronto, inalterado)</t>
+        </is>
+      </c>
+      <c r="B61" s="3">
+        <f>C61*$B$59</f>
+        <v/>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>+ Frete internacional + seguro</t>
+        </is>
+      </c>
+      <c r="B62" s="3">
+        <f>C62*$B$59</f>
+        <v/>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>80500</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>+ Despesas aduaneiras / importação</t>
+        </is>
+      </c>
+      <c r="B63" s="3">
+        <f>C63*$B$59</f>
+        <v/>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>+ Todos os impostos de importação (II, IPI, PIS/COFINS, ICMS)</t>
+        </is>
+      </c>
+      <c r="B64" s="3">
+        <f>C64*$B$59</f>
+        <v/>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>715700</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>POSTO NO BRASIL:</t>
+        </is>
+      </c>
+      <c r="B65" s="37">
+        <f>C65*$B$59</f>
+        <v/>
+      </c>
+      <c r="C65" s="38">
+        <f>SUM(C61:C64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>vs. o Preço Final ao Cliente de cada cenário (positivo = a unidade pronta importada custa mais)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Base (atual)</t>
+        </is>
+      </c>
+      <c r="B68" s="2">
+        <f>C65-E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sem imposto de importação (II)</t>
+        </is>
+      </c>
+      <c r="B69" s="2">
+        <f>C65-G33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1 conjunto de bateria</t>
+        </is>
+      </c>
+      <c r="B70" s="2">
+        <f>C65-I33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sem II + 1 conjunto de bateria</t>
+        </is>
+      </c>
+      <c r="B71" s="2">
+        <f>C65-K33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1" s="22">
+      <c r="A73" s="45" t="inlineStr">
+        <is>
+          <t>- Fonte: 'Planilha de Custos de Importacao - Pathfinder completo- Set 26.xlsx' (aba 'Pathfinder Pronto') - essa planilha NÃO está no repositório, então esses 5 valores foram transcritos do rodapé do slide MRS_Pathfinder_Simulation_Local_Taxes_Bilingual.pptx, não calculados ao vivo. Escopo diferente dos 4 cenários acima: é uma unidade pronta e já fabricada (sem margem da Wabtec Brasil, sem TP, sem reforma da Supermetal - é a importação direta de um produto completo), então não é uma 5ª coluna comparável 1-pra-1 com a tabela de cenários. Pegar a planilha-fonte pra deixar essa linha ao vivo.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A42:H42"/>
     <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A44:H44"/>
   </mergeCells>
   <dataValidations count="2">

--- a/Pathfinder_Cost_Summary_PT.xlsx
+++ b/Pathfinder_Cost_Summary_PT.xlsx
@@ -10767,7 +10767,7 @@
         <v/>
       </c>
       <c r="C61" s="2" t="n">
-        <v>900000</v>
+        <v>899999.9999999999</v>
       </c>
     </row>
     <row r="62">
@@ -10781,7 +10781,7 @@
         <v/>
       </c>
       <c r="C62" s="2" t="n">
-        <v>80500</v>
+        <v>80490</v>
       </c>
     </row>
     <row r="63">
@@ -10795,7 +10795,7 @@
         <v/>
       </c>
       <c r="C63" s="2" t="n">
-        <v>16800</v>
+        <v>16842.85660194175</v>
       </c>
     </row>
     <row r="64">
@@ -10809,7 +10809,7 @@
         <v/>
       </c>
       <c r="C64" s="2" t="n">
-        <v>715700</v>
+        <v>715697.9140243899</v>
       </c>
     </row>
     <row r="65">
@@ -10881,7 +10881,7 @@
     <row r="73" ht="60" customHeight="1" s="22">
       <c r="A73" s="45" t="inlineStr">
         <is>
-          <t>- Fonte: 'Planilha de Custos de Importacao - Pathfinder completo- Set 26.xlsx' (aba 'Pathfinder Pronto') - essa planilha NÃO está no repositório, então esses 5 valores foram transcritos do rodapé do slide MRS_Pathfinder_Simulation_Local_Taxes_Bilingual.pptx, não calculados ao vivo. Escopo diferente dos 4 cenários acima: é uma unidade pronta e já fabricada (sem margem da Wabtec Brasil, sem TP, sem reforma da Supermetal - é a importação direta de um produto completo), então não é uma 5ª coluna comparável 1-pra-1 com a tabela de cenários. Pegar a planilha-fonte pra deixar essa linha ao vivo.</t>
+          <t>- Fonte: lido AO VIVO de 'Planilha de Custos de Importacao - Pathfinder completo- Set 26.xlsx', aba 'Pathfinder Pronto' (celulas H24, I22, I26, I27, I28, I35, I56). Escopo diferente dos 4 cenários acima: é uma unidade pronta e já fabricada (sem margem da Wabtec Brasil, sem TP, sem reforma da Supermetal - é a importação direta de um produto completo), então não é uma 5ª coluna comparável 1-pra-1 com a tabela de cenários.</t>
         </is>
       </c>
     </row>
